--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755095296_individual_h_6.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755095296_individual_h_6.xlsx
@@ -658,7 +658,7 @@
         <v>0.008454177761639635</v>
       </c>
       <c r="C2" t="n">
-        <v>37877868</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>37877868</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>27421932</v>
+        <v>4243246</v>
       </c>
       <c r="L2" t="n">
-        <v>16060197</v>
+        <v>2200994</v>
       </c>
       <c r="M2" t="n">
-        <v>4027990</v>
+        <v>488437</v>
       </c>
       <c r="N2" t="n">
-        <v>208579</v>
+        <v>16792</v>
       </c>
       <c r="O2" t="n">
-        <v>2373437</v>
+        <v>290289</v>
       </c>
       <c r="P2" t="n">
-        <v>927265</v>
+        <v>115826</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999655485153198</v>
+        <v>0.9999961853027344</v>
       </c>
       <c r="R2" t="n">
-        <v>0.904990017414093</v>
+        <v>0.8246457576751709</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8036851286888123</v>
+        <v>0.6660070419311523</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7590407133102417</v>
+        <v>0.5812318325042725</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4304280877113342</v>
+        <v>0.1406801044940948</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8012396693229675</v>
+        <v>0.6383345127105713</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8739999532699585</v>
+        <v>0.7628763914108276</v>
       </c>
       <c r="X2" t="n">
-        <v>37877868</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>37877868</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>28872412</v>
+        <v>4796855</v>
       </c>
       <c r="AG2" t="n">
-        <v>17836630</v>
+        <v>2983951</v>
       </c>
       <c r="AH2" t="n">
-        <v>4798928</v>
+        <v>801380</v>
       </c>
       <c r="AI2" t="n">
-        <v>353991</v>
+        <v>59049</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2755108</v>
+        <v>459641</v>
       </c>
       <c r="AK2" t="n">
-        <v>1080323</v>
+        <v>180138</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9564692974090576</v>
+        <v>0.9560109972953796</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9113166332244873</v>
+        <v>0.9115679264068604</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8581637144088745</v>
+        <v>0.8585426211357117</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6622001528739929</v>
+        <v>0.6615541577339172</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020119309425354</v>
+        <v>0.9020492434501648</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314349889755249</v>
+        <v>0.9314607977867126</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002027047184025982</v>
       </c>
       <c r="C3" t="n">
-        <v>761</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>27421932</v>
+        <v>4243246</v>
       </c>
       <c r="E3" t="n">
-        <v>2681621</v>
+        <v>746751</v>
       </c>
       <c r="F3" t="n">
-        <v>41161</v>
+        <v>17113</v>
       </c>
       <c r="G3" t="n">
-        <v>4466</v>
+        <v>1589</v>
       </c>
       <c r="H3" t="n">
-        <v>2144</v>
+        <v>889</v>
       </c>
       <c r="I3" t="n">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="J3" t="n">
-        <v>60098426</v>
+        <v>10016598</v>
       </c>
       <c r="K3" t="n">
-        <v>64946573</v>
+        <v>10417700</v>
       </c>
       <c r="L3" t="n">
-        <v>74454168</v>
+        <v>11946575</v>
       </c>
       <c r="M3" t="n">
-        <v>91102576</v>
+        <v>15042656</v>
       </c>
       <c r="N3" t="n">
-        <v>97166603</v>
+        <v>16137685</v>
       </c>
       <c r="O3" t="n">
-        <v>94333026</v>
+        <v>15655190</v>
       </c>
       <c r="P3" t="n">
-        <v>96683896</v>
+        <v>16100158</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9094520211219788</v>
+        <v>0.8470215797424316</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8193796873092651</v>
+        <v>0.6711865663528442</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7197557687759399</v>
+        <v>0.5223740935325623</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3898738622665405</v>
+        <v>0.1879477053880692</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7766978144645691</v>
+        <v>0.5692622065544128</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7993491291999817</v>
+        <v>0.5987696647644043</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>28872412</v>
+        <v>4796855</v>
       </c>
       <c r="Z3" t="n">
-        <v>1187392</v>
+        <v>197460</v>
       </c>
       <c r="AA3" t="n">
-        <v>51135</v>
+        <v>8429</v>
       </c>
       <c r="AB3" t="n">
-        <v>40793</v>
+        <v>6823</v>
       </c>
       <c r="AC3" t="n">
-        <v>236</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>180</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>60099732</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>66511414</v>
+        <v>11099274</v>
       </c>
       <c r="AG3" t="n">
-        <v>76641422</v>
+        <v>12760866</v>
       </c>
       <c r="AH3" t="n">
-        <v>91588110</v>
+        <v>15262528</v>
       </c>
       <c r="AI3" t="n">
-        <v>97262032</v>
+        <v>16210047</v>
       </c>
       <c r="AJ3" t="n">
-        <v>94622500</v>
+        <v>15769750</v>
       </c>
       <c r="AK3" t="n">
-        <v>96738050</v>
+        <v>16122905</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575573801994324</v>
+        <v>0.9575310349464417</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9100120067596436</v>
+        <v>0.9099469780921936</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8575135469436646</v>
+        <v>0.8570606708526611</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6616765260696411</v>
+        <v>0.660917341709137</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9015980958938599</v>
+        <v>0.9013646841049194</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9312928318977356</v>
+        <v>0.9312344789505005</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03199143872576704</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>2717168</v>
+        <v>849668</v>
       </c>
       <c r="E4" t="n">
-        <v>16060197</v>
+        <v>2200994</v>
       </c>
       <c r="F4" t="n">
-        <v>740359</v>
+        <v>196146</v>
       </c>
       <c r="G4" t="n">
-        <v>28362</v>
+        <v>12367</v>
       </c>
       <c r="H4" t="n">
-        <v>50399</v>
+        <v>18349</v>
       </c>
       <c r="I4" t="n">
-        <v>3943</v>
+        <v>1734</v>
       </c>
       <c r="J4" t="n">
-        <v>1306</v>
+        <v>24</v>
       </c>
       <c r="K4" t="n">
-        <v>2878879</v>
+        <v>902292</v>
       </c>
       <c r="L4" t="n">
-        <v>3922998</v>
+        <v>1103767</v>
       </c>
       <c r="M4" t="n">
-        <v>1278695</v>
+        <v>351911</v>
       </c>
       <c r="N4" t="n">
-        <v>276006</v>
+        <v>102571</v>
       </c>
       <c r="O4" t="n">
-        <v>588769</v>
+        <v>164471</v>
       </c>
       <c r="P4" t="n">
-        <v>133679</v>
+        <v>36002</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999827742576599</v>
+        <v>0.9999980926513672</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9072155356407166</v>
+        <v>0.8356839418411255</v>
       </c>
       <c r="S4" t="n">
-        <v>0.811456561088562</v>
+        <v>0.668586790561676</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7388764619827271</v>
+        <v>0.5502334237098694</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4091485142707825</v>
+        <v>0.1609145700931549</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7887779474258423</v>
+        <v>0.6018229126930237</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8350093960762024</v>
+        <v>0.6709338426589966</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1226769</v>
+        <v>206052</v>
       </c>
       <c r="Z4" t="n">
-        <v>17836630</v>
+        <v>2983951</v>
       </c>
       <c r="AA4" t="n">
-        <v>496804</v>
+        <v>82537</v>
       </c>
       <c r="AB4" t="n">
-        <v>32965</v>
+        <v>5520</v>
       </c>
       <c r="AC4" t="n">
-        <v>6858</v>
+        <v>1130</v>
       </c>
       <c r="AD4" t="n">
-        <v>408</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1314038</v>
+        <v>220718</v>
       </c>
       <c r="AG4" t="n">
-        <v>1735744</v>
+        <v>289476</v>
       </c>
       <c r="AH4" t="n">
-        <v>793161</v>
+        <v>132039</v>
       </c>
       <c r="AI4" t="n">
-        <v>180577</v>
+        <v>30209</v>
       </c>
       <c r="AJ4" t="n">
-        <v>299295</v>
+        <v>49911</v>
       </c>
       <c r="AK4" t="n">
-        <v>79525</v>
+        <v>13255</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9570130109786987</v>
+        <v>0.9567704200744629</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.910663902759552</v>
+        <v>0.9107567667961121</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.85783851146698</v>
+        <v>0.8578009605407715</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6619382500648499</v>
+        <v>0.6612355709075928</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018049240112305</v>
+        <v>0.9017068147659302</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313638806343079</v>
+        <v>0.9313476085662842</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>361</v>
+        <v>12</v>
       </c>
       <c r="D5" t="n">
-        <v>102777</v>
+        <v>36075</v>
       </c>
       <c r="E5" t="n">
-        <v>1065296</v>
+        <v>299261</v>
       </c>
       <c r="F5" t="n">
-        <v>4027990</v>
+        <v>488437</v>
       </c>
       <c r="G5" t="n">
-        <v>98941</v>
+        <v>32820</v>
       </c>
       <c r="H5" t="n">
-        <v>280289</v>
+        <v>70833</v>
       </c>
       <c r="I5" t="n">
-        <v>20675</v>
+        <v>7595</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>2730216</v>
+        <v>766362</v>
       </c>
       <c r="L5" t="n">
-        <v>3540237</v>
+        <v>1078264</v>
       </c>
       <c r="M5" t="n">
-        <v>1568339</v>
+        <v>446596</v>
       </c>
       <c r="N5" t="n">
-        <v>326412</v>
+        <v>72552</v>
       </c>
       <c r="O5" t="n">
-        <v>682368</v>
+        <v>219650</v>
       </c>
       <c r="P5" t="n">
-        <v>232760</v>
+        <v>77614</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999866485595703</v>
+        <v>0.9999985098838806</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9427512288093567</v>
+        <v>0.897814154624939</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9238271117210388</v>
+        <v>0.866375744342804</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9709420204162598</v>
+        <v>0.9511006474494934</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9938514828681946</v>
+        <v>0.9892757534980774</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9870262742042542</v>
+        <v>0.9764770269393921</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9962599873542786</v>
+        <v>0.9930423498153687</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>48155</v>
+        <v>8093</v>
       </c>
       <c r="Z5" t="n">
-        <v>510890</v>
+        <v>85757</v>
       </c>
       <c r="AA5" t="n">
-        <v>4798928</v>
+        <v>801380</v>
       </c>
       <c r="AB5" t="n">
-        <v>59714</v>
+        <v>9985</v>
       </c>
       <c r="AC5" t="n">
-        <v>174844</v>
+        <v>29185</v>
       </c>
       <c r="AD5" t="n">
-        <v>3798</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1279736</v>
+        <v>212753</v>
       </c>
       <c r="AG5" t="n">
-        <v>1763804</v>
+        <v>295307</v>
       </c>
       <c r="AH5" t="n">
-        <v>797401</v>
+        <v>133653</v>
       </c>
       <c r="AI5" t="n">
-        <v>181000</v>
+        <v>30295</v>
       </c>
       <c r="AJ5" t="n">
-        <v>300697</v>
+        <v>50298</v>
       </c>
       <c r="AK5" t="n">
-        <v>79702</v>
+        <v>13302</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735268950462341</v>
+        <v>0.9734548926353455</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9642821550369263</v>
+        <v>0.9641887545585632</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837660789489746</v>
+        <v>0.9837294220924377</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963095784187317</v>
+        <v>0.9962948560714722</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938762187957764</v>
+        <v>0.9938633441925049</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.998374879360199</v>
+        <v>0.9983736872673035</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>78</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>57053</v>
+        <v>15191</v>
       </c>
       <c r="E6" t="n">
-        <v>97115</v>
+        <v>21162</v>
       </c>
       <c r="F6" t="n">
-        <v>117427</v>
+        <v>25485</v>
       </c>
       <c r="G6" t="n">
-        <v>208579</v>
+        <v>16792</v>
       </c>
       <c r="H6" t="n">
-        <v>50704</v>
+        <v>9645</v>
       </c>
       <c r="I6" t="n">
-        <v>4035</v>
+        <v>1066</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>38779</v>
+        <v>6517</v>
       </c>
       <c r="Z6" t="n">
-        <v>32116</v>
+        <v>5368</v>
       </c>
       <c r="AA6" t="n">
-        <v>65335</v>
+        <v>10940</v>
       </c>
       <c r="AB6" t="n">
-        <v>353991</v>
+        <v>59049</v>
       </c>
       <c r="AC6" t="n">
-        <v>41884</v>
+        <v>6989</v>
       </c>
       <c r="AD6" t="n">
-        <v>2886</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>1713</v>
+        <v>1294</v>
       </c>
       <c r="E7" t="n">
-        <v>74729</v>
+        <v>34313</v>
       </c>
       <c r="F7" t="n">
-        <v>364759</v>
+        <v>106751</v>
       </c>
       <c r="G7" t="n">
-        <v>136184</v>
+        <v>51703</v>
       </c>
       <c r="H7" t="n">
-        <v>2373437</v>
+        <v>290289</v>
       </c>
       <c r="I7" t="n">
-        <v>104963</v>
+        <v>25589</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>167</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>4860</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>177905</v>
+        <v>29802</v>
       </c>
       <c r="AB7" t="n">
-        <v>45512</v>
+        <v>7615</v>
       </c>
       <c r="AC7" t="n">
-        <v>2755108</v>
+        <v>459641</v>
       </c>
       <c r="AD7" t="n">
-        <v>72253</v>
+        <v>12043</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>80</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>168</v>
+        <v>64</v>
       </c>
       <c r="E8" t="n">
-        <v>4237</v>
+        <v>2280</v>
       </c>
       <c r="F8" t="n">
-        <v>14989</v>
+        <v>6416</v>
       </c>
       <c r="G8" t="n">
-        <v>8053</v>
+        <v>4092</v>
       </c>
       <c r="H8" t="n">
-        <v>205233</v>
+        <v>64755</v>
       </c>
       <c r="I8" t="n">
-        <v>927265</v>
+        <v>115826</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>168</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>486</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>1982</v>
+        <v>331</v>
       </c>
       <c r="AB8" t="n">
-        <v>1593</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>75473</v>
+        <v>12596</v>
       </c>
       <c r="AD8" t="n">
-        <v>1080323</v>
+        <v>180138</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
